--- a/output/full_scan/batch_seq5_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-30.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>900.2403485021662</v>
+        <v>1205.240348502166</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>549</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>71.50153799157223</v>
+        <v>71.50153799998033</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29.91590967680843</v>
+        <v>29.91590966588272</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.624034850216613</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
@@ -574,27 +574,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4934</v>
+        <v>5483</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>840.0485646078388</v>
+        <v>1016.648782670683</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.4</v>
+        <v>180</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.12849895667974</v>
+        <v>59.6750489786832</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18.16263245391604</v>
+        <v>27.24055168527494</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.906649860785881</v>
+        <v>1.373818267578388</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.05044069752099</v>
+        <v>-0.365517691266092</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5471</v>
+        <v>4934</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>765.8003207416211</v>
+        <v>1010.048564607839</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>61.6</v>
+        <v>18.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.16833965004052</v>
+        <v>58.1284989530559</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>37.70329461873968</v>
+        <v>18.16263241339742</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6333639271075052</v>
+        <v>1.906649860785881</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0499209466065551</v>
+        <v>0.0504406975400695</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5299</v>
+        <v>5471</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>747.8573491918296</v>
+        <v>1000.800320741621</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>123</v>
+        <v>61.6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.13491853068974</v>
+        <v>62.16833967026197</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>36.98940570965661</v>
+        <v>37.70329455100656</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.105994627080249</v>
+        <v>0.6333639271075052</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4692994472986438</v>
+        <v>0.0499209465779362</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5314</v>
+        <v>5536</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>741.4699207498034</v>
+        <v>988.5600146403827</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>66.8</v>
+        <v>1290</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.16013440959099</v>
+        <v>61.58064084379667</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6.16307464003008</v>
+        <v>32.71086933856168</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.45419161489581</v>
+        <v>0.736664600890109</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.8945702584897579</v>
+        <v>1.586778574170282</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5536</v>
+        <v>5314</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>738.5600146403829</v>
+        <v>944.2290762194438</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1290</v>
+        <v>66.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.58064083546986</v>
+        <v>57.16013451998445</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.71086932581221</v>
+        <v>6.163074680774853</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.736664600890109</v>
+        <v>4.648070059499219</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.586778574742638</v>
+        <v>0.8945702575357832</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4952</v>
+        <v>6121</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>731.9779741616566</v>
+        <v>938.4177385013642</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>57.5</v>
+        <v>417.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.105527011482</v>
+        <v>57.03341772449866</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.87425080829445</v>
+        <v>26.22374594804841</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.549037084591081</v>
+        <v>1.597182661495601</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0049861468394534</v>
+        <v>-1.24222585521677</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5483</v>
+        <v>5460</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>731.6487826706834</v>
+        <v>924</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>180</v>
+        <v>15.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.67504895216814</v>
+        <v>57.24124700275895</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.24055169919127</v>
+        <v>22.97448063922684</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.373818267578388</v>
+        <v>7.577121398067703</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.3655176908845057</v>
+        <v>0.0167767531831462</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6121</v>
+        <v>6139</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>723.4177385013642</v>
+        <v>910.3613897213404</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>417.5</v>
+        <v>923</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,29 +976,29 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.03341768551054</v>
+        <v>63.40265042262038</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.22374591858861</v>
+        <v>24.58914828111834</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.597182661495601</v>
+        <v>1.450379548523282</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-1.24222585521677</v>
+        <v>11.18612599915935</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>691.4070530356508</v>
+        <v>891.4070530356508</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>166.5</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>69.5951029891954</v>
+        <v>69.59510294980501</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.68245395028712</v>
+        <v>31.68245399892729</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.740705303565086</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.761692532743105</v>
+        <v>2.761692533220069</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4931</v>
+        <v>5228</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>678.8811353488132</v>
+        <v>885.7060591200719</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>239</v>
+        <v>67.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>51.09513883691815</v>
+        <v>54.5879240780534</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.41564608183981</v>
+        <v>39.68037137710417</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1901237397278357</v>
+        <v>0.560239451206028</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-5.189572971585866</v>
+        <v>-2.000832353369733</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6109</v>
+        <v>5347</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>亞元</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>663.8797968366247</v>
+        <v>860.8619050959649</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.61638817709073</v>
+        <v>66.3872667260457</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.99495221520396</v>
+        <v>25.51365313680412</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.031436212357351</v>
+        <v>1.026875550117962</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1490208752319911</v>
+        <v>4.184787407315016</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5460</v>
+        <v>5269</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>658.8683864279878</v>
+        <v>851.3440991252029</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.7</v>
+        <v>1470</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.24124708690648</v>
+        <v>54.34418496680863</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.97448061279372</v>
+        <v>13.33392689887308</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2942122274581502</v>
+        <v>0.9816904591712896</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0167767531640665</v>
+        <v>0.9100622039124868</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6155</v>
+        <v>4952</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>651.1949878632699</v>
+        <v>846.9779741616566</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.93680255229412</v>
+        <v>57.10552703170902</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>48.35198903003872</v>
+        <v>26.87425081600504</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3950056984557527</v>
+        <v>2.549037084591081</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.9446524366692336</v>
+        <v>0.0049861468012939</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5302</v>
+        <v>5371</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>649.1603661449079</v>
+        <v>844</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.65</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.94703033093883</v>
+        <v>69.35446357067597</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>35.47190978711936</v>
+        <v>18.32891559306674</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4422933778622117</v>
+        <v>5.478163098555512</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0443002054176574</v>
+        <v>1.433397189190496</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4958</v>
+        <v>4554</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>645.2018342187087</v>
+        <v>828.7773038044583</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>630</v>
+        <v>31.55</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.89646338633394</v>
+        <v>58.87503963313449</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.9725477389398</v>
+        <v>29.19472962765542</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9830694338849008</v>
+        <v>0.3657133802664259</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-4.271307604485777</v>
+        <v>0.1531063470700353</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5371</v>
+        <v>5469</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>624</v>
+        <v>828.0409065022067</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>69.3544635316905</v>
+        <v>57.73163731925676</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18.32891559518257</v>
+        <v>17.94636932037916</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5.478163098555512</v>
+        <v>1.604090650220666</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.433397189343121</v>
+        <v>0.4484608043866933</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4924</v>
+        <v>4958</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>617.4543152401378</v>
+        <v>815.2122048054721</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.25</v>
+        <v>630</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.10271290525208</v>
+        <v>63.89646338867043</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.8255225509399</v>
+        <v>27.97254770520579</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.816011207532273</v>
+        <v>0.9839937032000012</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1536317901394689</v>
+        <v>-4.271307604390429</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5245</v>
+        <v>6155</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>615.6204938202612</v>
+        <v>806.1949878632699</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>27.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.91615455462595</v>
+        <v>61.93680255414684</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.16283236716908</v>
+        <v>48.35198896309897</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5150230723478669</v>
+        <v>0.3950056984557527</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.009761808136673201</v>
+        <v>-0.9446524366501664</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6126</v>
+        <v>5328</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>信音</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>612.2626041213899</v>
+        <v>800.834162463713</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>35.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>43.60316832395852</v>
+        <v>74.84828744602861</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.13375361993441</v>
+        <v>44.80364750105917</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.1653036967334769</v>
+        <v>0.7523395385083008</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.8418168401806712</v>
+        <v>1.789065779450985</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5230</v>
+        <v>4924</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>608.2675727669306</v>
+        <v>787.4543152401378</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21.45</v>
+        <v>14.25</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.2277147356698</v>
+        <v>64.10271289872405</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>37.30327929617785</v>
+        <v>28.82552298213172</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.090160090642918</v>
+        <v>2.816011207532273</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2630497152083502</v>
+        <v>0.1536317900917708</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6113</v>
+        <v>5230</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>亞矽</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>608.2276946768997</v>
+        <v>778.2675727669306</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>27.45</v>
+        <v>21.45</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.71641356334794</v>
+        <v>58.22771475988405</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.99800299926726</v>
+        <v>37.3032793449866</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4192739829502256</v>
+        <v>1.090160090642918</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.2945497891196302</v>
+        <v>0.2630497151988129</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5228</v>
+        <v>6116</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>605.7060591200719</v>
+        <v>771.8583637675989</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>67.2</v>
+        <v>19.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.58792359244784</v>
+        <v>61.88273694505919</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.68036995960005</v>
+        <v>31.22827472599667</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.560239451206028</v>
+        <v>1.304576870633767</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.000832350479198</v>
+        <v>-0.0723497604624796</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5426</v>
+        <v>5302</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>604.4056593817256</v>
+        <v>759.1603661449079</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>31.3</v>
+        <v>12.65</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.07733391173814</v>
+        <v>55.94703036279066</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>35.1774040659005</v>
+        <v>35.47190982912365</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4203398730976352</v>
+        <v>0.4422933778622117</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.9379508264830124</v>
+        <v>0.04430020540621</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6116</v>
+        <v>5474</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>601.8583637675989</v>
+        <v>759.1306018746758</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19.6</v>
+        <v>168</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.88273694422111</v>
+        <v>47.34564002942155</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.22827471498244</v>
+        <v>20.39169481710863</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.304576870633767</v>
+        <v>0.3293854037516189</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.07234976047774121</v>
+        <v>-2.15924693341589</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5328</v>
+        <v>5299</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>600.834162463713</v>
+        <v>747.8573491918296</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>123</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>74.84828744345015</v>
+        <v>59.1349185488436</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44.80364751250459</v>
+        <v>36.98940564884202</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7523395385083008</v>
+        <v>1.105994627080249</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.7890657794319</v>
+        <v>0.4692994473177236</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6139</v>
+        <v>4904</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>595.3613897213403</v>
+        <v>728.4241801678126</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>923</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>63.40265041403246</v>
+        <v>52.48268618178249</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24.58914825646711</v>
+        <v>29.38047092044462</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.450379548523282</v>
+        <v>1.242418016781259</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>11.1861259993501</v>
+        <v>-0.6107176604917073</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4577</v>
+        <v>6113</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>592.1676190357083</v>
+        <v>718.2276946768997</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>92.2</v>
+        <v>27.45</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>40.9658396781822</v>
+        <v>52.71641363971527</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.10907032041611</v>
+        <v>30.99800297402644</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3843883802083964</v>
+        <v>0.4192739829502256</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.549210327765198</v>
+        <v>-0.2945497893867406</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4976</v>
+        <v>4542</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>588.4680167716546</v>
+        <v>716.2150938379649</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>37.5</v>
+        <v>449.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.3483289679775</v>
+        <v>70.79744239032512</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>39.50850260162315</v>
+        <v>43.11388333307388</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2802648304919367</v>
+        <v>0.1752733206814089</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,51 +2054,51 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1498608256466154</v>
+        <v>4.011010273388834</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4987</v>
+        <v>6114</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>科誠</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>584.8800228060524</v>
+        <v>700.0209649231276</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>30.65</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.06266580150494</v>
+        <v>54.43218466649928</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.90740217602925</v>
+        <v>21.37040686400888</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.750864911342356</v>
+        <v>2.368304699743203</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,11 +2107,11 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0408812918967312</v>
+        <v>0.0357710413501209</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>583.934148299872</v>
+        <v>698.934148299872</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>86.8</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.00567275308843</v>
+        <v>49.00567276817337</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17.98324319201944</v>
+        <v>17.98324328480384</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.673320427162594</v>
@@ -2154,37 +2154,37 @@
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.9068359324505528</v>
+        <v>-0.90683593258411</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4554</v>
+        <v>5353</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>583.7773038044584</v>
+        <v>694.8804434666162</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>31.55</v>
+        <v>31.85</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.87503959685942</v>
+        <v>55.55196989651156</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.1947296818621</v>
+        <v>54.73961844401963</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3657133802664259</v>
+        <v>0.5268387464926888</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1531063471272753</v>
+        <v>-0.2748670191058904</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5236</v>
+        <v>4939</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>583.334154743544</v>
+        <v>692.649006080089</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>168.5</v>
+        <v>64.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.56024997901633</v>
+        <v>61.22092861878722</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.68742815546532</v>
+        <v>33.03894452100007</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4218953816767323</v>
+        <v>0.7852848094120043</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2796937863397795</v>
+        <v>-0.8705042878971314</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5488</v>
+        <v>4931</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>松普</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>581.5940018537659</v>
+        <v>678.8811353488132</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>13</v>
+        <v>239</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.63487509998161</v>
+        <v>51.09513882976931</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.18892593523545</v>
+        <v>25.41564599798442</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4053185160801757</v>
+        <v>0.1901237397278357</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0609372697578204</v>
+        <v>-5.189572971719439</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5285</v>
+        <v>4903</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>界霖</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>577.7031372721672</v>
+        <v>673.2038435021763</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>96.3</v>
+        <v>40.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>56.52154318440252</v>
+        <v>46.0676910556979</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>48.27842436572836</v>
+        <v>12.73458533299913</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.92987832060288</v>
+        <v>0.9149917981887792</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.3918927494705162</v>
+        <v>0.2308865024806363</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5469</v>
+        <v>6109</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>亞元</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>573.0409065022067</v>
+        <v>663.8797968366247</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89.3</v>
+        <v>13</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.73163729878873</v>
+        <v>62.61638819147093</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.9463693314519</v>
+        <v>23.99495221520395</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.604090650220666</v>
+        <v>1.031436212357351</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.448460804367608</v>
+        <v>0.1490208752300844</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6153</v>
+        <v>6142</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>友勁</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>572.753960028799</v>
+        <v>661.5150258851284</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>21.45</v>
+        <v>9.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.24842788753777</v>
+        <v>60.92713224621224</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.90427890670984</v>
+        <v>24.13729584729996</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2845905593252763</v>
+        <v>0.5254348989390801</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.2863456758764244</v>
+        <v>0.0528634272232087</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5269</v>
+        <v>4916</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>566.3440991252029</v>
+        <v>657.0755534673162</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1470</v>
+        <v>102.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.34418483401996</v>
+        <v>52.77121598868501</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.33392690574657</v>
+        <v>25.73057994673249</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9816904591712896</v>
+        <v>0.7904840397209681</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.910062211544048</v>
+        <v>-2.371925038885841</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6103</v>
+        <v>5356</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>565.0866926531146</v>
+        <v>655.7843625446627</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>31.1</v>
+        <v>27.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.41432315820736</v>
+        <v>53.75061523316464</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6.998007674202704</v>
+        <v>23.17815904423342</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4991917847294855</v>
+        <v>0.5634041247208007</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2447084545438713</v>
+        <v>-0.0947899940455027</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5353</v>
+        <v>4545</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>554.8804434666163</v>
+        <v>643.6672996589152</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31.85</v>
+        <v>37.25</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.55196990079352</v>
+        <v>53.463856204663</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>54.73961839206974</v>
+        <v>32.52215722404427</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5268387464926888</v>
+        <v>0.2372372122827087</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.2748670191058904</v>
+        <v>-0.2691928168196077</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>4989</v>
+        <v>5245</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>548.1918107858153</v>
+        <v>635.6204938202612</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>87.3</v>
+        <v>27.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.32019084353168</v>
+        <v>54.91615457010607</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.02719478835657</v>
+        <v>29.16283238363618</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5012676842265578</v>
+        <v>0.5150230723478669</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1066171803865501</v>
+        <v>-0.009761808155752999</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4973</v>
+        <v>5381</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>547.9174314208699</v>
+        <v>634.9361426653684</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>173.5</v>
+        <v>28.05</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.75537825921416</v>
+        <v>49.17041551528967</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>40.11690059756428</v>
+        <v>24.15997199006512</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4984128039181338</v>
+        <v>0.0959030151397909</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-5.078627985474782</v>
+        <v>-0.3431832917225209</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>5347</v>
+        <v>5450</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>寶聯通</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>545.8619050959649</v>
+        <v>627.2083736196577</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>216</v>
+        <v>14.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>66.38726670008816</v>
+        <v>57.91384810908181</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.51365303678264</v>
+        <v>40.45589753540899</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.026875550117962</v>
+        <v>0.5535226692287003</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>4.184787407772966</v>
+        <v>0.011265002568929</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6114</v>
+        <v>5278</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>540.0209649231277</v>
+        <v>621.6535347029665</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>30.65</v>
+        <v>24.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.43218411479985</v>
+        <v>55.85038554548461</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.37040684070368</v>
+        <v>19.74967564405141</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.368304699743203</v>
+        <v>0.8225412425019986</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0357710418271083</v>
+        <v>0.0478580199846513</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>5474</v>
+        <v>5340</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>534.1306018746758</v>
+        <v>619.6586180003487</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>168</v>
+        <v>95.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.34563997038978</v>
+        <v>49.73936000602105</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.3916948134593</v>
+        <v>13.43920473132671</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3293854037516189</v>
+        <v>1.386408095292163</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.159246933129702</v>
+        <v>0.8013294750433619</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4545</v>
+        <v>6126</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>信音</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>528.6672996589152</v>
+        <v>612.2626041213899</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>37.25</v>
+        <v>35.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.4638561868921</v>
+        <v>43.60316833693263</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32.52215731452358</v>
+        <v>28.13375363847478</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2372372122827087</v>
+        <v>0.1653036967334769</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.2691928175255434</v>
+        <v>-0.8418168401806712</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>4939</v>
+        <v>5222</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>亞電</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>522.6490060800888</v>
+        <v>608.0002997570394</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>64.3</v>
+        <v>126.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>61.22092861664873</v>
+        <v>58.31147938289035</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>33.03894452100005</v>
+        <v>18.16976387695845</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7852848094120043</v>
+        <v>2.857446140808325</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.8705042878875995</v>
+        <v>1.312739789797362</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>5381</v>
+        <v>5392</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>519.9361426653684</v>
+        <v>606.3229988167835</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>28.05</v>
+        <v>45.75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.17041562891927</v>
+        <v>54.74964512144581</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.15997214659696</v>
+        <v>11.1536468547855</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.0959030151397909</v>
+        <v>0.5518883407873739</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3431832922674988</v>
+        <v>0.1134405377219804</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>4542</v>
+        <v>5251</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>科嶠</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>516.2150938379649</v>
+        <v>605.7209662935293</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>449.5</v>
+        <v>32.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>70.79744238255444</v>
+        <v>56.72123264023772</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>43.11388341632464</v>
+        <v>35.13683289217835</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1752733206814089</v>
+        <v>0.2986358353045878</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>4.011010273674991</v>
+        <v>0.0677338778411663</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, cci_momentum, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5356</v>
+        <v>5426</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>515.7843625446627</v>
+        <v>604.4056593817256</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>27.6</v>
+        <v>31.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.75061531532248</v>
+        <v>53.07733394353946</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.17815919440789</v>
+        <v>35.17740405426313</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5634041247208007</v>
+        <v>0.4203398730976352</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0947899940836627</v>
+        <v>-0.9379508265784092</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>5450</v>
+        <v>5488</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>寶聯通</t>
+          <t>松普</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>512.2083736196578</v>
+        <v>601.5940018537659</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.91384809383857</v>
+        <v>56.63487510384083</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>40.45589751675202</v>
+        <v>22.18892596044564</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5535226692287003</v>
+        <v>0.4053185160801757</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0112650025784675</v>
+        <v>-0.0609372697425559</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>5340</v>
+        <v>4577</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>504.6586180003487</v>
+        <v>592.1676190357083</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>95.7</v>
+        <v>92.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.7393599881115</v>
+        <v>40.96583968457419</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.43920474374247</v>
+        <v>24.10907030942355</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.386408095292163</v>
+        <v>0.3843883802083964</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.8013294750242728</v>
+        <v>1.549210327717494</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>4903</v>
+        <v>4976</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>503.2038435021763</v>
+        <v>588.4680167716546</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>40.5</v>
+        <v>37.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.06769106240047</v>
+        <v>53.34832898222913</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.73458531372788</v>
+        <v>39.50850258186405</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9149917981887792</v>
+        <v>0.2802648304919367</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2308865023661568</v>
+        <v>-0.1498608256466154</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>4916</v>
+        <v>6120</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>502.0755534673162</v>
+        <v>587.7014485460548</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.5</v>
+        <v>14.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.77121600258342</v>
+        <v>54.06036609319587</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.73057994666592</v>
+        <v>13.643998690454</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7904840397209681</v>
+        <v>0.8154972646481901</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-2.371925039305588</v>
+        <v>-0.0376110192881528</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6142</v>
+        <v>5243</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>友勁</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>501.5150258851284</v>
+        <v>586.9954210155693</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9.4</v>
+        <v>102</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>60.92713223547176</v>
+        <v>42.65861884736488</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.13729584225051</v>
+        <v>12.78778359794319</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5254348989390801</v>
+        <v>0.4408328239608591</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,51 +3432,51 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0528634272213006</v>
+        <v>-1.336953747845476</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4945</v>
+        <v>5452</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陞達科技</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>490.5710737637258</v>
+        <v>586.2379843813803</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.15235053416068</v>
+        <v>52.99826684260505</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.97481257574066</v>
+        <v>9.186369010567567</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4265127663271301</v>
+        <v>1.186407965549033</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,11 +3485,11 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.5457915156162878</v>
+        <v>-0.0752135083875978</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>475.1118978114034</v>
+        <v>585.1118978114034</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>27.8</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.19638202794635</v>
+        <v>48.19638200153852</v>
       </c>
       <c r="I58" s="2" t="n">
         <v>32.0213987766228</v>
@@ -3529,7 +3529,7 @@
         <v>0.8400785202902198</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,48 +3538,48 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0485899387513118</v>
+        <v>-0.0485899387894709</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>5452</v>
+        <v>4987</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>佶優</t>
+          <t>科誠</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>471.2379843813804</v>
+        <v>584.8800228060522</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>34.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.99826681027667</v>
+        <v>55.06266638851235</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.186368973879487</v>
+        <v>23.90740201432822</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.186407965549033</v>
+        <v>0.750864911342356</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0752135084257553</v>
+        <v>-0.0408812909091187</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>5386</v>
+        <v>5236</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>470.236702003936</v>
+        <v>583.334154743544</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>472</v>
+        <v>168.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.33551721672215</v>
+        <v>50.56025004816581</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.23518623291032</v>
+        <v>20.68742817669047</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4506448626783306</v>
+        <v>0.4218953816767323</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-5.850123545813213</v>
+        <v>0.27969378567198</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>5251</v>
+        <v>6115</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>465.7209662935758</v>
+        <v>578.8556671003253</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>32.1</v>
+        <v>48.25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>56.7212326813147</v>
+        <v>50.33855368983401</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>35.13683258190489</v>
+        <v>10.99123764156129</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2986358353045878</v>
+        <v>0.5781405906774223</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0677338776789939</v>
+        <v>-0.101763453082017</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>5243</v>
+        <v>5285</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>界霖</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>451.9954210155693</v>
+        <v>577.7031372721672</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102</v>
+        <v>96.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.65861882230973</v>
+        <v>56.52154318841419</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.78778361244202</v>
+        <v>48.27842433523888</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4408328239608591</v>
+        <v>0.92987832060288</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.336953747769157</v>
+        <v>-0.3918927494800623</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>5278</v>
+        <v>6153</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>451.6535347029665</v>
+        <v>572.753960028799</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>24.8</v>
+        <v>21.45</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.8503854558584</v>
+        <v>51.24842789692016</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.7496756513176</v>
+        <v>25.90427882955501</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8225412425019986</v>
+        <v>0.2845905593252763</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.047858019994189</v>
+        <v>-0.2863456758573479</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>4956</v>
+        <v>5484</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>451.5925998244138</v>
+        <v>569.0651956039711</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>38.4</v>
+        <v>45.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.11760481773515</v>
+        <v>46.78547302709379</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.67378708563248</v>
+        <v>25.54335212947198</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5471180068420353</v>
+        <v>0.2232464296022986</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0739724451448002</v>
+        <v>-0.8435173662486367</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>5345</v>
+        <v>4973</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>廣穎</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>446.9675107719001</v>
+        <v>567.9174314208699</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>26.7</v>
+        <v>173.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.52661968472172</v>
+        <v>53.75537826924542</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.20474769771482</v>
+        <v>40.11690057130873</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.056594448412157</v>
+        <v>0.4984128039181338</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.7404796464071852</v>
+        <v>-5.078627985541559</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6115</v>
+        <v>6103</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>438.8556671003253</v>
+        <v>565.0866926531146</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>48.25</v>
+        <v>31.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.33855363639641</v>
+        <v>51.41432316315365</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10.99123764156128</v>
+        <v>6.998007676283933</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5781405906774223</v>
+        <v>0.4991917847294855</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.101763453062938</v>
+        <v>0.244708454496174</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>5439</v>
+        <v>4989</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>438.1955064423534</v>
+        <v>563.1918107858153</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>310.5</v>
+        <v>87.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>36.12952984002019</v>
+        <v>48.32019084353168</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.84724179043128</v>
+        <v>18.02719478835657</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2831725578821524</v>
+        <v>0.5012676842265578</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.602639297988606</v>
+        <v>0.1066171803865501</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>5481</v>
+        <v>4956</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>438.1299518310242</v>
+        <v>561.5925998244138</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21.1</v>
+        <v>38.4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.54973413828516</v>
+        <v>44.11760480759731</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.03367173755558</v>
+        <v>15.67378715377953</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4776912536290514</v>
+        <v>0.5471180068420353</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0003491806058744</v>
+        <v>-0.07397244517342159</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>5392</v>
+        <v>4938</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>436.3229988167835</v>
+        <v>545.0919106755464</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>45.75</v>
+        <v>83.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.74964510028396</v>
+        <v>47.1116302530868</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.15364681442587</v>
+        <v>17.13921263611362</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5518883407873739</v>
+        <v>0.5439149603255884</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1134405377696787</v>
+        <v>-0.8821730433690462</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>5484</v>
+        <v>5315</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>429.0651956039712</v>
+        <v>541.5183723206031</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>45.7</v>
+        <v>23.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.78547298034422</v>
+        <v>55.69106201610477</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25.54335209011409</v>
+        <v>19.40105099939694</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2232464296022986</v>
+        <v>0.8020536803172037</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.8435173661627751</v>
+        <v>0.0268775535068752</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>5222</v>
+        <v>4943</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>428.0002997570394</v>
+        <v>535.8091771129647</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>126.5</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>58.31147929373024</v>
+        <v>55.93011034064799</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.16976376227354</v>
+        <v>13.43887581183028</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.857446140808325</v>
+        <v>2.0948768729265</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.312739790465148</v>
+        <v>0.0720808363614707</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>4968</v>
+        <v>5205</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>424.7260669246729</v>
+        <v>531.1686919162775</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>115.5</v>
+        <v>24.1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.49634858116343</v>
+        <v>51.97800817302917</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.90367999183782</v>
+        <v>18.70797405311028</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.789233668458095</v>
+        <v>1.286968428409439</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4102671686936333</v>
+        <v>-0.0094764874919147</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>4904</v>
+        <v>4760</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>423.3892161669329</v>
+        <v>528.5026860811562</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>105</v>
+        <v>344</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.48268614443885</v>
+        <v>47.4241468012133</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>29.38047079493993</v>
+        <v>21.8740856324177</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.238921616693291</v>
+        <v>0.4883232563566194</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.610717660243679</v>
+        <v>-10.42271368745547</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6120</v>
+        <v>4972</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>417.7014485460547</v>
+        <v>522.8161159057695</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>14.8</v>
+        <v>16.85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.06036609319587</v>
+        <v>55.40332554693133</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.64399869024917</v>
+        <v>27.46241526059015</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8154972646481901</v>
+        <v>0.7976569229885717</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0376110193371999</v>
+        <v>0.0145882494046094</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>5457</v>
+        <v>6124</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>414.4049259549115</v>
+        <v>515.5524508060271</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>34.15</v>
+        <v>30.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.85941329608796</v>
+        <v>48.52719821746921</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23.08518700194321</v>
+        <v>23.32749738950002</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3176410299212447</v>
+        <v>0.1115204986172728</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0793103724745035</v>
+        <v>-0.1372675942393941</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4760</v>
+        <v>5493</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>413.5026860811561</v>
+        <v>502.7403460510392</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>344</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.42414679667994</v>
+        <v>48.72889022745925</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.87408569442292</v>
+        <v>16.25784794537379</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4883232563566194</v>
+        <v>0.2497704971450114</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-10.42271368726465</v>
+        <v>-0.3643726472324181</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>5498</v>
+        <v>5443</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>410.5645432494405</v>
+        <v>500.6710095816357</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>60.8</v>
+        <v>115.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.83619144649342</v>
+        <v>54.7203274539966</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.89385680647647</v>
+        <v>18.70648167599489</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2776085988806162</v>
+        <v>2.399890421242607</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.5808266950561487</v>
+        <v>0.9034243791400622</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>4972</v>
+        <v>5225</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>407.8161159057695</v>
+        <v>494.0610215212228</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.85</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>55.40332543695133</v>
+        <v>44.86618080426954</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>27.46241510478992</v>
+        <v>16.11623033725929</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7976569229885717</v>
+        <v>0.4026475215581179</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,51 +4598,51 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0145882494141495</v>
+        <v>-0.0354501329587724</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>5315</v>
+        <v>4945</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>陞達科技</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>401.5183723206033</v>
+        <v>490.5710737637258</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>23.1</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.6910618265533</v>
+        <v>54.2771034398348</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.40105102612517</v>
+        <v>12.94982402254239</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8020536803172037</v>
+        <v>0.4265127663271301</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0268775535736562</v>
+        <v>0.5460282206590492</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>5289</v>
+        <v>5386</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>385.5140453920316</v>
+        <v>490.236702003936</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1615</v>
+        <v>472</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.9151661010338</v>
+        <v>44.33551722470795</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.84569097413413</v>
+        <v>16.23518617288634</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7223993887430167</v>
+        <v>0.4506448626783306</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-49.04884820631116</v>
+        <v>-5.850123545946778</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6124</v>
+        <v>5348</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>380.5524508060271</v>
+        <v>490.204350606052</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>30.35</v>
+        <v>16.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.52719821394933</v>
+        <v>51.98571518648099</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.32749742536418</v>
+        <v>10.70868254573748</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1115204986172728</v>
+        <v>2.037673550391087</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1372675942775507</v>
+        <v>0.494513084830066</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>5225</v>
+        <v>4974</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>379.0610215212228</v>
+        <v>480.7780634280445</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.86618048693041</v>
+        <v>39.10643164681231</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.11623030273105</v>
+        <v>22.79834190932012</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4026475215581179</v>
+        <v>0.3569876918153778</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0354501324817929</v>
+        <v>-0.6227893918269347</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>4949</v>
+        <v>4912</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>375.0141846222297</v>
+        <v>470.7898883249065</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>77.5</v>
+        <v>86.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>34.65392630676628</v>
+        <v>40.83249914519078</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.46245105788839</v>
+        <v>20.90585017705321</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7288682437615162</v>
+        <v>0.411517214930011</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.525279617637747</v>
+        <v>-0.6817297262450337</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>4943</v>
+        <v>4927</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>365.8091771129647</v>
+        <v>460.6377627022191</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>48.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>55.93011038967524</v>
+        <v>45.6328660230758</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.43887581183028</v>
+        <v>12.0694931532908</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.0948768729265</v>
+        <v>0.7406424943999441</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0720808363233106</v>
+        <v>-0.4898716947854458</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>4749</v>
+        <v>4919</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>364.1606556594288</v>
+        <v>448.0868274661229</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>875</v>
+        <v>173.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>37.98421254507531</v>
+        <v>47.52342620479348</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.01428064334256</v>
+        <v>18.01212303916634</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8477772028639898</v>
+        <v>0.551041324648712</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-8.587480330297659</v>
+        <v>-3.277956075432656</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>5493</v>
+        <v>5345</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>362.7403460510392</v>
+        <v>446.9675107719001</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>91</v>
+        <v>26.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.7288903181004</v>
+        <v>48.52661967278768</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.25784815571534</v>
+        <v>15.20474768830353</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.2497704971450114</v>
+        <v>1.056594448412157</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3643726480528388</v>
+        <v>-0.7404796463308663</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>5205</v>
+        <v>4960</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>361.1686919162775</v>
+        <v>440.0311477112321</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>24.1</v>
+        <v>26.15</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.97800822932772</v>
+        <v>33.69552313171732</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.70797407131167</v>
+        <v>20.2051224993472</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.286968428409439</v>
+        <v>0.5310135002499218</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.009476487673167701</v>
+        <v>-0.3048997931140347</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>4938</v>
+        <v>5439</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>355.0919106755464</v>
+        <v>438.1955064423534</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>83.8</v>
+        <v>310.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.11163021695948</v>
+        <v>36.1295299205115</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.13921262953166</v>
+        <v>21.84724173057306</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5439149603255884</v>
+        <v>0.2831725578821524</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.8821730432545632</v>
+        <v>-2.602639298751782</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>5215</v>
+        <v>5481</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>348.8784457932017</v>
+        <v>438.1299518310242</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>43.75</v>
+        <v>21.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.35643409168864</v>
+        <v>53.54976382798814</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.10641752731617</v>
+        <v>30.03370197555958</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2137232659303692</v>
+        <v>0.4776912536290514</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.3583021074603106</v>
+        <v>0.0003491574573309</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>4906</v>
+        <v>4966</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>343.4619810663592</v>
+        <v>425.5227014658028</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>42.7</v>
+        <v>629</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.11290304310891</v>
+        <v>39.86481328721226</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.07058591028579</v>
+        <v>15.73351433576924</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3983463786579705</v>
+        <v>0.744472579106331</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.6053828279547928</v>
+        <v>-9.405242015423566</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>5292</v>
+        <v>4968</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>342.9401319776875</v>
+        <v>424.7260669246728</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>219.5</v>
+        <v>115.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,49 +5269,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.42597041312664</v>
+        <v>52.49634858116343</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.59653757266069</v>
+        <v>14.90367999252279</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5504599131922591</v>
+        <v>0.789233668458095</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.258122906561407</v>
+        <v>0.4102671689798295</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>4908</v>
+        <v>5490</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>342.1049480865715</v>
+        <v>420.0733833119494</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>189</v>
+        <v>28.55</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.92716197282408</v>
+        <v>48.37414337042312</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.71670858564185</v>
+        <v>19.16586016268036</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4834302753940889</v>
+        <v>0.7058682385262326</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-2.680184443791532</v>
+        <v>-0.08539797774381661</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>5272</v>
+        <v>5457</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>340.4651335639041</v>
+        <v>414.4049259549115</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>21.2</v>
+        <v>34.15</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.82517525737205</v>
+        <v>49.85941334867433</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.10742872309042</v>
+        <v>23.08518697408742</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4003777792118344</v>
+        <v>0.3176410299212447</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0139423823432304</v>
+        <v>-0.0793103725317346</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>5438</v>
+        <v>5498</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>339.1199798143329</v>
+        <v>410.5645432494405</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>18.55</v>
+        <v>60.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.50522560677809</v>
+        <v>43.83619145098901</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.24089972402594</v>
+        <v>12.89385680982467</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6833501443973665</v>
+        <v>0.2776085988806162</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0653895404427893</v>
+        <v>-0.5808266950694894</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4967</v>
+        <v>4588</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>338.1420210837465</v>
+        <v>407.2708731919988</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>263.5</v>
+        <v>58.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.29668470583858</v>
+        <v>50.93492562658894</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.86363412379516</v>
+        <v>16.644032874424</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5696038132097386</v>
+        <v>0.2731059572706478</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-2.339833034082201</v>
+        <v>-0.1063187077453487</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>4912</v>
+        <v>4582</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>335.7898883249065</v>
+        <v>403.2577307935105</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>86.5</v>
+        <v>25.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.83249907663698</v>
+        <v>44.6685478105536</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.90585017416128</v>
+        <v>11.57077459474036</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.411517214930011</v>
+        <v>0.366823139591552</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.681729726054245</v>
+        <v>0.1405274835844692</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>5475</v>
+        <v>5291</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>331.5544822556602</v>
+        <v>399.8377515990164</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>244.5</v>
+        <v>59.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.79309757333058</v>
+        <v>41.58190824980486</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.2185767700406</v>
+        <v>27.44942147332205</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.678366415810159</v>
+        <v>0.3856294044142911</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.064404777973273</v>
+        <v>-0.9211480023912464</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>5443</v>
+        <v>6108</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>330.6710095816356</v>
+        <v>398.1029344395595</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>115.5</v>
+        <v>18.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>54.72032741876766</v>
+        <v>48.34465074086722</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.7064816815706</v>
+        <v>10.10565813988665</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.399890421242607</v>
+        <v>1.468716245557731</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.903424379349941</v>
+        <v>-0.07755443249387819</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4960</v>
+        <v>5234</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>330.0311477112321</v>
+        <v>393.5787743124099</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.15</v>
+        <v>390.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>33.69552313536748</v>
+        <v>47.47917021380296</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.2051224996151</v>
+        <v>17.40908242659149</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5310135002499218</v>
+        <v>0.877771880237517</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.3048997931331194</v>
+        <v>0.5877104378481555</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>4951</v>
+        <v>5287</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>323.9426125524989</v>
+        <v>390.538680432525</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>96.3</v>
+        <v>148</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.88269049666119</v>
+        <v>47.14068124660628</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25.91569137270483</v>
+        <v>14.42793869042774</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5579843681765313</v>
+        <v>0.8399402035567447</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.7079392099572845</v>
+        <v>0.3979950792097557</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6104</v>
+        <v>5220</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>321.4389875006357</v>
+        <v>389.8323777630917</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>102.5</v>
+        <v>21</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.94450078193558</v>
+        <v>42.58919543369576</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.53584752050061</v>
+        <v>21.21420054013769</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.340530811595063</v>
+        <v>0.4119782396653494</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2392692442886043</v>
+        <v>-0.1114498635357606</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>4919</v>
+        <v>5289</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>318.0868274661229</v>
+        <v>385.5140453920316</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>173.5</v>
+        <v>1615</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.52342619092507</v>
+        <v>42.91516610725623</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.01212306383659</v>
+        <v>20.8456909313632</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.551041324648712</v>
+        <v>0.7223993887430167</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-3.277956075051097</v>
+        <v>-49.04884820592945</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>4966</v>
+        <v>4942</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>315.423263487151</v>
+        <v>379.5914502813656</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>629</v>
+        <v>37.65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.86481322424441</v>
+        <v>49.36946578574197</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.73351430727783</v>
+        <v>11.38210925322355</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7331840028459673</v>
+        <v>0.270599732235173</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-9.405242013515569</v>
+        <v>-0.0192384290376668</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6117</v>
+        <v>4961</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>314.8759372155131</v>
+        <v>376.3433679922317</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>73.5</v>
+        <v>165</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,49 +5958,49 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.29743264741219</v>
+        <v>45.26363729050094</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.03244229729371</v>
+        <v>15.89571900440524</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2620958380658911</v>
+        <v>1.13940900199524</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M104" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.4546262034899131</v>
+        <v>-0.875358788402034</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>4927</v>
+        <v>4949</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>300.6377627022191</v>
+        <v>375.0141846222298</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>48.2</v>
+        <v>77.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.63286599382904</v>
+        <v>34.65392633120985</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.06949317287583</v>
+        <v>19.46245111902972</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7406424943999441</v>
+        <v>0.7288682437615162</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.4898716947663706</v>
+        <v>-1.52527961809566</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>4588</v>
+        <v>5344</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>292.2708731919988</v>
+        <v>373.5950989183759</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>58.8</v>
+        <v>15.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>50.93492553342006</v>
+        <v>46.25248688725515</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.64403279585351</v>
+        <v>14.75935701125928</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2731059572706478</v>
+        <v>0.6240292290023975</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.106318707421001</v>
+        <v>-0.048818108160124</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>5348</v>
+        <v>4729</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>290.204350606052</v>
+        <v>367.8382293437742</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16.5</v>
+        <v>22.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.98571516648591</v>
+        <v>49.83148115353551</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.70868244487564</v>
+        <v>19.09808872386393</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.037673550391087</v>
+        <v>0.6314553503140101</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.49451308499224</v>
+        <v>-0.1677164140230097</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>5291</v>
+        <v>4749</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>289.8377515990164</v>
+        <v>364.1606556594289</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>59.4</v>
+        <v>875</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.58190824468908</v>
+        <v>37.98421256377676</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>27.44942146181107</v>
+        <v>17.01428058547309</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3856294044142911</v>
+        <v>0.8477772028639898</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.9211480024294092</v>
+        <v>-8.587480328771377</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4905</v>
+        <v>4967</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>288.0422014644958</v>
+        <v>363.1420210837465</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0</v>
+        <v>263.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>7.517903615242218</v>
+        <v>43.29668466930165</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>25.53624105809048</v>
+        <v>13.86363400223958</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.0074006105503704</v>
+        <v>0.5696038132097386</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-4.769826500874256</v>
+        <v>-2.33983303362426</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6108</v>
+        <v>5274</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>283.1029344395595</v>
+        <v>358.6628741567627</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>18.8</v>
+        <v>16495</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.34465073398054</v>
+        <v>44.9444654383064</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.10565813988665</v>
+        <v>19.13094539303705</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.468716245557731</v>
+        <v>1.088468088133457</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.07755443249387819</v>
+        <v>-359.5549647338121</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>5309</v>
+        <v>4906</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>282.5378991641324</v>
+        <v>358.4619810663592</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>63</v>
+        <v>42.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.43929981655889</v>
+        <v>48.11290303986488</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.52302203782734</v>
+        <v>21.07058584834206</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.1773930707251552</v>
+        <v>0.3983463786579705</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.166032665603166</v>
+        <v>-0.6053828279261734</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4585</v>
+        <v>5388</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>中磊</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>280.9609372348179</v>
+        <v>351.2968055117678</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>300.5</v>
+        <v>80.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.86608274747376</v>
+        <v>46.03572274673252</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>22.80268298300419</v>
+        <v>14.32019112285236</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3245015478827214</v>
+        <v>0.6767910267890936</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-1.89764137886628</v>
+        <v>-0.8691094991603806</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>5490</v>
+        <v>4933</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>280.0733833119494</v>
+        <v>350.2849572258747</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>28.55</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.37414320965542</v>
+        <v>44.59503044552454</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.16586008009492</v>
+        <v>15.11616020332594</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7058682385262326</v>
+        <v>0.5882814167834858</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0853979776388787</v>
+        <v>-0.4148069801759109</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>5287</v>
+        <v>5215</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>275.538680432525</v>
+        <v>348.8784457932017</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>148</v>
+        <v>43.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.14068115999227</v>
+        <v>47.35643411351863</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.42793865633809</v>
+        <v>22.1064175052237</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8399402035567447</v>
+        <v>0.2137232659303692</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.3979950792097557</v>
+        <v>-0.3583021074889341</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>5220</v>
+        <v>5292</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>274.8323777630916</v>
+        <v>342.9401319776875</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>21</v>
+        <v>219.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.58919537283323</v>
+        <v>49.42597045338187</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>21.21420053650167</v>
+        <v>14.59653755623257</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4119782396653494</v>
+        <v>0.5504599131922591</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1114498635262188</v>
+        <v>-0.2581229062752044</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>4974</v>
+        <v>4908</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>270.7780634280444</v>
+        <v>342.1049480865715</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>70.2</v>
+        <v>189</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>39.10643152702298</v>
+        <v>42.92716197112493</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.79834192629343</v>
+        <v>16.71670854655518</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3569876918153778</v>
+        <v>0.4834302753940889</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.6227893915407317</v>
+        <v>-2.68018444348628</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6125</v>
+        <v>6104</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>269.6417764594358</v>
+        <v>341.4389875006357</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>59.5</v>
+        <v>102.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.19936916887008</v>
+        <v>51.94450091065906</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.77837607723307</v>
+        <v>14.53584753028218</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3401605671838297</v>
+        <v>0.340530811595063</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.5849568609192066</v>
+        <v>-0.2392692441931942</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5344</v>
+        <v>6136</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>263.5950989183759</v>
+        <v>340.9734827419829</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>15.6</v>
+        <v>25.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.25248693739668</v>
+        <v>47.19953252919456</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.75935701125927</v>
+        <v>11.55960516712522</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6240292290023975</v>
+        <v>0.3819536504841639</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0488181082078221</v>
+        <v>-0.0325126389403759</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>5274</v>
+        <v>5272</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>263.5112070325634</v>
+        <v>340.4651335639041</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16495</v>
+        <v>21.2</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.94446543005987</v>
+        <v>45.82517532492073</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.13094539642945</v>
+        <v>12.1074287555081</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.078166851624824</v>
+        <v>0.4003777792118344</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-359.5549647061471</v>
+        <v>0.0139423822764512</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>4582</v>
+        <v>5438</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>263.2577307935105</v>
+        <v>339.1199798143329</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>25.55</v>
+        <v>18.55</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.66854779280352</v>
+        <v>42.50522569503145</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.57077459474036</v>
+        <v>19.2408997044225</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.366823139591552</v>
+        <v>0.6833501443973665</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1405274835558523</v>
+        <v>-0.0653895405000299</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>4979</v>
+        <v>6117</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>261.7967230629877</v>
+        <v>334.8759372155131</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>474</v>
+        <v>73.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.30821336690073</v>
+        <v>39.29743271574003</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.84295493893126</v>
+        <v>21.03244228827574</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.13794910186953</v>
+        <v>0.2620958380658911</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-8.752143145929693</v>
+        <v>-0.454626203680708</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4961</v>
+        <v>6128</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>261.3433679922317</v>
+        <v>332.7450667000704</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>165</v>
+        <v>20.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.26363717540566</v>
+        <v>54.18526829905137</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.89571900654457</v>
+        <v>20.41946424226453</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.13940900199524</v>
+        <v>0.3063616932135274</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.8753587881158291</v>
+        <v>-0.035585877176546</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>5234</v>
+        <v>5475</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>253.5787743124095</v>
+        <v>331.5544822556602</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>390.5</v>
+        <v>244.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.47917018535404</v>
+        <v>43.79309757349129</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.40908241982573</v>
+        <v>18.21857678168239</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.877771880237517</v>
+        <v>0.678366415810159</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.5877104381343212</v>
+        <v>0.06440477796372331</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5355</v>
+        <v>4994</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>245.603121706724</v>
+        <v>331.535565993934</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6.21</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.31585283295983</v>
+        <v>53.05021495821419</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.54703358577288</v>
+        <v>25.72629942377167</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4560644999468878</v>
+        <v>0.3490221806408769</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0775240200486728</v>
+        <v>0.4412596441934655</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4971</v>
+        <v>6112</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>243.7004840738559</v>
+        <v>330.3582203135167</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>491</v>
+        <v>45</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>35.64764746224343</v>
+        <v>49.35147572732021</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.90268668972213</v>
+        <v>18.31027075493441</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4340248547455424</v>
+        <v>0.6241233765069715</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-5.730469356823868</v>
+        <v>-0.3574009278772853</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>4942</v>
+        <v>4951</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>239.5914502813656</v>
+        <v>323.9426125524989</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>37.65</v>
+        <v>96.3</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>49.36946561654025</v>
+        <v>38.88269052129998</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.38210921264562</v>
+        <v>25.91569134299758</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.270599732235173</v>
+        <v>0.5579843681765313</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0192384290376668</v>
+        <v>-0.7079392099572845</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4729</v>
+        <v>4915</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>232.8382293437742</v>
+        <v>323.7025311792316</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>22.7</v>
+        <v>66</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,49 +7177,49 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>49.83148112186952</v>
+        <v>29.28474708118124</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.09808870654478</v>
+        <v>17.20148358750622</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6314553503140101</v>
+        <v>1.026719373300969</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M127" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.1677164139943895</v>
+        <v>-1.2139191796996</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>4999</v>
+        <v>6152</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>231.1080191993024</v>
+        <v>304.5329924256777</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>20.1</v>
+        <v>13.65</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>42.57132273139436</v>
+        <v>40.53944878154796</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.17932136950638</v>
+        <v>12.46846954097038</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.3384812807073487</v>
+        <v>0.4055305179663149</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0594289802271977</v>
+        <v>-0.1236384749401781</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>4994</v>
+        <v>4585</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>216.5355659939341</v>
+        <v>300.9609372348179</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>300.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>53.05021483395159</v>
+        <v>39.8660828273458</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>25.72629832045724</v>
+        <v>22.80268298300419</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.3490221806408769</v>
+        <v>0.3245015478827214</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.441259645242835</v>
+        <v>-1.8976413802019</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4977</v>
+        <v>6125</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>212.4626494926871</v>
+        <v>289.6417764594358</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>169.5</v>
+        <v>59.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>42.02613440694308</v>
+        <v>46.19936923498373</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>8.564020501125947</v>
+        <v>16.77837609388032</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.3622749965313531</v>
+        <v>0.3401605671838297</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.328526508267739</v>
+        <v>-0.5849568609764396</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>4915</v>
+        <v>4905</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>208.7025311792317</v>
+        <v>288.0422014644958</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>29.28474694491895</v>
+        <v>7.517903625151476</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.20148363555885</v>
+        <v>25.53624109213188</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.026719373300969</v>
+        <v>0.0074006105503704</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-1.213919179623279</v>
+        <v>-4.769826501313082</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>5258</v>
+        <v>5309</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>203.4820997554194</v>
+        <v>282.5378991641324</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>48.85</v>
+        <v>63</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45.19681664346347</v>
+        <v>40.43929983866568</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16.79754899034722</v>
+        <v>17.5230219964255</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.4281349543530129</v>
+        <v>0.1773930707251552</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.1822858746366986</v>
+        <v>-1.166032665669951</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>6136</v>
+        <v>5203</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>200.9734827419829</v>
+        <v>269.6956617652504</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>25.2</v>
+        <v>67.3</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>47.19953250068738</v>
+        <v>48.20337861066854</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>11.55960519174471</v>
+        <v>17.57063605063332</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.3819536504841639</v>
+        <v>0.7554261594695649</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0325126389785346</v>
+        <v>-0.3178492252350638</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>5388</v>
+        <v>5355</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>中磊</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>191.2968055117677</v>
+        <v>265.6031217067239</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>80.8</v>
+        <v>6.21</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>46.03572280324654</v>
+        <v>41.31585266318498</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>14.32019103755831</v>
+        <v>13.54703373212106</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.6767910267890936</v>
+        <v>0.4560644999468878</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.8691094995610498</v>
+        <v>-0.07752401993991929</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>4909</v>
+        <v>4979</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>190.3779159352351</v>
+        <v>261.7967230629889</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>44.85</v>
+        <v>474</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>31.85727099950299</v>
+        <v>40.30821337269341</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>31.64806264198637</v>
+        <v>13.84295487980411</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.4369706079502752</v>
+        <v>1.13794910186953</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.3582365702151555</v>
+        <v>-8.752143145929693</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>6112</v>
+        <v>4971</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>190.3582203135165</v>
+        <v>243.700484073852</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>45</v>
+        <v>491</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>49.35147562021747</v>
+        <v>35.64764748733495</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>18.31027076177906</v>
+        <v>18.90268674345971</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.6241233765069715</v>
+        <v>0.4340248547455424</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.3574009276101757</v>
+        <v>-5.730469357300827</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>6152</v>
+        <v>4999</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>189.5329924256777</v>
+        <v>231.1080191993024</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>13.65</v>
+        <v>20.1</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>40.53944878953393</v>
+        <v>42.57132282655122</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>12.4684694964061</v>
+        <v>16.17932138616692</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.4055305179663149</v>
+        <v>0.3384812807073487</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.1236384749344535</v>
+        <v>-0.0594289802653545</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5244</v>
+        <v>4909</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>177.2096859420902</v>
+        <v>210.3779159352351</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>35.9</v>
+        <v>44.85</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>35.95571800162168</v>
+        <v>31.85727106647427</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>11.83765051664446</v>
+        <v>31.64806261610351</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.4640473323521979</v>
+        <v>0.4369706079502752</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.1269797096373264</v>
+        <v>-0.3582365703677874</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>6128</v>
+        <v>6123</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>172.7450667000703</v>
+        <v>207.8939937831579</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>20.8</v>
+        <v>41.75</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>54.18526826624979</v>
+        <v>35.20490087983254</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>20.41946422715138</v>
+        <v>19.48555862298765</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.3063616932135274</v>
+        <v>0.4893993783157906</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.0355858771479285</v>
+        <v>-0.3754042775365078</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>4995</v>
+        <v>5223</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>172.3560521487167</v>
+        <v>204.0278334961637</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>44.8</v>
+        <v>25</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>47.1622723239504</v>
+        <v>45.69635921613794</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>17.2778675918748</v>
+        <v>11.24256714597708</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.3866525655519492</v>
+        <v>1.023024947224063</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.156016320769936</v>
+        <v>-0.07250552363857179</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>6133</v>
+        <v>5258</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>164.6798670941017</v>
+        <v>203.4820997554194</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>22.35</v>
+        <v>48.85</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>44.94791825271136</v>
+        <v>45.19681667158816</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>10.98176563476026</v>
+        <v>16.79754900244713</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.2836347654431346</v>
+        <v>0.4281349543530129</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.1823853266722276</v>
+        <v>-0.182285874560381</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>4935</v>
+        <v>4977</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>159.5671821605656</v>
+        <v>202.4626494926871</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>36.6</v>
+        <v>169.5</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>40.81822632394865</v>
+        <v>42.02613441787592</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.72072293846836</v>
+        <v>8.564020601256891</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.4743997725805319</v>
+        <v>0.3622749965313531</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.4482816722948856</v>
+        <v>-1.328526508439449</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>6118</v>
+        <v>5244</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>158.2033707239608</v>
+        <v>177.2096859420902</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>16.9</v>
+        <v>35.9</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45.4874942362308</v>
+        <v>35.9557179670838</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>15.20854115776147</v>
+        <v>11.83765052167445</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.9260208829315768</v>
+        <v>0.4640473323521979</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0633788739844267</v>
+        <v>-0.1269797094560785</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5203</v>
+        <v>4995</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>154.6956617652503</v>
+        <v>172.3560521487167</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>67.3</v>
+        <v>44.8</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>48.20337848116296</v>
+        <v>47.162272162678</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>17.5706356795124</v>
+        <v>17.27786760406839</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.7554261594695649</v>
+        <v>0.3866525655519492</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.3178492258074548</v>
+        <v>-0.1560163204837489</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>5465</v>
+        <v>6133</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>153.4360723158545</v>
+        <v>164.6798670941017</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>24.9</v>
+        <v>22.35</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>40.91376609299143</v>
+        <v>44.94791828647797</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>17.74422660752564</v>
+        <v>10.9817656039234</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.8191934840687174</v>
+        <v>0.2836347654431346</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.1962853547319507</v>
+        <v>-0.1823853266817644</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>4933</v>
+        <v>4935</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>125.2849572258747</v>
+        <v>159.5671821605656</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.5950303650411</v>
+        <v>40.81822631230984</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>15.11616016049246</v>
+        <v>17.72072299239699</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.5882814167834858</v>
+        <v>0.4743997725805319</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.4148069799660419</v>
+        <v>-0.4482816722185626</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>6123</v>
+        <v>6118</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>建達</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>92.89399378315792</v>
+        <v>158.2033707239608</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>41.75</v>
+        <v>16.9</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>35.20490085404985</v>
+        <v>45.48749428824453</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>19.48555860558725</v>
+        <v>15.20854113906807</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.4893993783157906</v>
+        <v>0.9260208829315768</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.3754042775555934</v>
+        <v>-0.06337887401304799</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>5223</v>
+        <v>5465</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>89.02783349616394</v>
+        <v>153.4360723158532</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45.69635208813665</v>
+        <v>40.91376621286833</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>11.24256315196497</v>
+        <v>17.74422662892234</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.023024947224063</v>
+        <v>0.8191934840687174</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,11 +8308,11 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.07250551914536039</v>
+        <v>-0.1962853546651735</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
